--- a/output/full_scan/batch_seq8_2026-09-11.xlsx
+++ b/output/full_scan/batch_seq8_2026-09-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -633,21 +633,21 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7717</v>
+        <v>6933</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>747.3431875509878</v>
+        <v>837.7295542522916</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>517</v>
+        <v>320</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>62.79067322155656</v>
+        <v>69.75046458913428</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12.84872987377097</v>
+        <v>49.2238222491884</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.834318755098773</v>
+        <v>0.5502687953039851</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>11.36920330481673</v>
+        <v>4.748262238741873</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6885</v>
+        <v>7717</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>725.3264018710335</v>
+        <v>747.3431875509878</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>27.1</v>
+        <v>517</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>75.41563753626374</v>
+        <v>62.79067322155656</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>51.81551205894348</v>
+        <v>12.84872987377097</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.632640187103348</v>
+        <v>2.834318755098773</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4562845778616697</v>
+        <v>11.36920330481673</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6924</v>
+        <v>6885</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>721.4831664171143</v>
+        <v>725.3264018710335</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>141.5</v>
+        <v>27.1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>74.21958124113179</v>
+        <v>75.41563753626374</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>30.82727052007288</v>
+        <v>51.81551205894348</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.748316641711422</v>
+        <v>2.632640187103348</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.405694920412</v>
+        <v>0.4562845778616697</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7810</v>
+        <v>6924</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>714.5031475174357</v>
+        <v>721.4831664171143</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>219.5</v>
+        <v>141.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.70607557779378</v>
+        <v>74.21958124113179</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34.42329061909368</v>
+        <v>30.82727052007288</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.380440643074208</v>
+        <v>1.748316641711422</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.0987608924232326</v>
+        <v>2.405694920412</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6840</v>
+        <v>7810</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>691.0334250374486</v>
+        <v>714.5031475174357</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>89</v>
+        <v>219.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>56.97219153724772</v>
+        <v>59.70607557779378</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>40.09035604494094</v>
+        <v>34.42329061909368</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.4754126563261275</v>
+        <v>1.380440643074208</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.9622764758406516</v>
+        <v>-0.0987608924232326</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7792</v>
+        <v>6840</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>685.4204817900892</v>
+        <v>691.0334250374486</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>305.5</v>
+        <v>89</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>60.60401231839802</v>
+        <v>56.97219153724772</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>52.40002050287073</v>
+        <v>40.09035604494094</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.6339265032411227</v>
+        <v>0.4754126563261275</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.9891514167548509</v>
+        <v>-0.9622764758406516</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6957</v>
+        <v>7792</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>657.875586262728</v>
+        <v>685.4204817900892</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>231.5</v>
+        <v>305.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>62.04696334553351</v>
+        <v>60.60401231839802</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13.23650341667664</v>
+        <v>52.40002050287073</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.048329008433871</v>
+        <v>0.6339265032411227</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.8066261648553605</v>
+        <v>-0.9891514167548509</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7828</v>
+        <v>6957</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>639.4271155573555</v>
+        <v>657.875586262728</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1975</v>
+        <v>231.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>58.43431876801625</v>
+        <v>62.04696334553351</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>22.12683886242788</v>
+        <v>13.23650341667664</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.9099241366973234</v>
+        <v>2.048329008433871</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>38.71783446630566</v>
+        <v>0.8066261648553605</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7711</v>
+        <v>7828</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>634.7132090934626</v>
+        <v>639.4271155573555</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>531</v>
+        <v>1975</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>52.53434325612884</v>
+        <v>58.43431876801625</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>48.02251390019974</v>
+        <v>22.12683886242788</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.1954832659839128</v>
+        <v>0.9099241366973234</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-4.456476180279807</v>
+        <v>38.71783446630566</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7799</v>
+        <v>7711</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>633.4609012849785</v>
+        <v>634.7132090934626</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>414.5</v>
+        <v>531</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>61.29133697370161</v>
+        <v>52.53434325612884</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>20.35764416721978</v>
+        <v>48.02251390019974</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.306576104904521</v>
+        <v>0.1954832659839128</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>6.421966960922023</v>
+        <v>-4.456476180279807</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6861</v>
+        <v>7799</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>629</v>
+        <v>633.4609012849785</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>214.5</v>
+        <v>414.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.53664816690835</v>
+        <v>61.29133697370161</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>19.03734313184145</v>
+        <v>20.35764416721978</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6.281938587125421</v>
+        <v>3.306576104904521</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>4.310846486374059</v>
+        <v>6.421966960922023</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6909</v>
+        <v>6861</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>607.0443863289655</v>
+        <v>629</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>43.9</v>
+        <v>214.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>61.66696453095565</v>
+        <v>56.53664816690835</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>16.48090215959306</v>
+        <v>19.03734313184145</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4.095789740723524</v>
+        <v>6.281938587125421</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.3929503933406636</v>
+        <v>4.310846486374059</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7714</v>
+        <v>6909</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>581.9977872070805</v>
+        <v>607.0443863289655</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>173.5</v>
+        <v>43.9</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.80581277776805</v>
+        <v>61.66696453095565</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>17.50857382130317</v>
+        <v>16.48090215959306</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.480021916527978</v>
+        <v>4.095789740723524</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-1.06024203607642</v>
+        <v>0.3929503933406636</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6983</v>
+        <v>8021</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>579.3158446005989</v>
+        <v>605.8279473552901</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>345.5</v>
+        <v>418.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>56.71665938927312</v>
+        <v>47.76245898729814</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>26.60484715998041</v>
+        <v>10.56192091887487</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.2645696394895362</v>
+        <v>0.1593605056943745</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.914122086104104</v>
+        <v>0.7901625151138636</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6887</v>
+        <v>7714</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>553.8872575096988</v>
+        <v>581.9977872070805</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>37.35</v>
+        <v>173.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>50.46266592269528</v>
+        <v>55.80581277776805</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>27.76950011061153</v>
+        <v>17.50857382130317</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.2857122449125363</v>
+        <v>1.480021916527978</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.058784251330551</v>
+        <v>-1.06024203607642</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7703</v>
+        <v>6983</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>548.1942355806526</v>
+        <v>579.3158446005989</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>200</v>
+        <v>345.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>62.85004800510252</v>
+        <v>56.71665938927312</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>20.09600708040798</v>
+        <v>26.60484715998041</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.8420140621349603</v>
+        <v>0.2645696394895362</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>2.687413973832626</v>
+        <v>1.914122086104104</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7744</v>
+        <v>6887</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>539.169768138918</v>
+        <v>553.8872575096988</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>497</v>
+        <v>37.35</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>49.56667146793526</v>
+        <v>50.46266592269528</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>34.92932529146137</v>
+        <v>27.76950011061153</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.7423293321401754</v>
+        <v>0.2857122449125363</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-2.767156584276776</v>
+        <v>-0.058784251330551</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6913</v>
+        <v>7703</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>522.2388490360634</v>
+        <v>548.1942355806526</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>128.5</v>
+        <v>200</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>38.34748026157795</v>
+        <v>62.85004800510252</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>22.93968360087135</v>
+        <v>20.09600708040798</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.530028995667632</v>
+        <v>0.8420140621349603</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-3.639031516400622</v>
+        <v>2.687413973832626</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6969</v>
+        <v>7744</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>504.8581327309579</v>
+        <v>539.169768138918</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>33.65</v>
+        <v>497</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>50.045968727721</v>
+        <v>49.56667146793526</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>23.07222836813662</v>
+        <v>34.92932529146137</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8545328993366722</v>
+        <v>0.7423293321401754</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.204500109810351</v>
+        <v>-2.767156584276776</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6925</v>
+        <v>6913</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>503.5934717034654</v>
+        <v>522.2388490360634</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>50.2</v>
+        <v>128.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>43.60455827295097</v>
+        <v>38.34748026157795</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9.171320569452904</v>
+        <v>22.93968360087135</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.779163707623385</v>
+        <v>0.530028995667632</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.160106835745283</v>
+        <v>-3.639031516400622</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7788</v>
+        <v>6969</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>492.892065917713</v>
+        <v>504.8581327309579</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>286.5</v>
+        <v>33.65</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>50.51392990550579</v>
+        <v>50.045968727721</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>30.01821630741947</v>
+        <v>23.07222836813662</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6754709983544351</v>
+        <v>0.8545328993366722</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-2.509952141688679</v>
+        <v>-0.204500109810351</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6906</v>
+        <v>6925</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>487.5991658686001</v>
+        <v>503.5934717034654</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>80.7</v>
+        <v>50.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.30292727470187</v>
+        <v>43.60455827295097</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>36.64671635335772</v>
+        <v>9.171320569452904</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.1881046671778238</v>
+        <v>1.779163707623385</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.6013576903154263</v>
+        <v>0.160106835745283</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6895</v>
+        <v>7788</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>475.5332606059575</v>
+        <v>492.892065917713</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>153</v>
+        <v>286.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>59.36811404783072</v>
+        <v>50.51392990550579</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.63690326614281</v>
+        <v>30.01821630741947</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.1753488338575367</v>
+        <v>0.6754709983544351</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1947049487340129</v>
+        <v>-2.509952141688679</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7631</v>
+        <v>6906</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>474.9977154655917</v>
+        <v>487.5991658686001</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>138</v>
+        <v>80.7</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>42.77763804496025</v>
+        <v>55.30292727470187</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20.83139989434061</v>
+        <v>36.64671635335772</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.736850436223801</v>
+        <v>0.1881046671778238</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.826479836638393</v>
+        <v>0.6013576903154263</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6937</v>
+        <v>6895</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>468.1014386381746</v>
+        <v>475.5332606059575</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>288.5</v>
+        <v>153</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>54.6053206185696</v>
+        <v>59.36811404783072</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>16.52758920725688</v>
+        <v>31.63690326614281</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.9322671015168928</v>
+        <v>0.1753488338575367</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.056224956175033</v>
+        <v>0.1947049487340129</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7402</v>
+        <v>7631</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>455.1860943825759</v>
+        <v>474.9977154655917</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>100.5</v>
+        <v>138</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>41.11291313334426</v>
+        <v>42.77763804496025</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15.26474406961505</v>
+        <v>20.83139989434061</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7818365222393238</v>
+        <v>1.736850436223801</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.8634944022999251</v>
+        <v>-0.826479836638393</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8028</v>
+        <v>6937</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>444.1529791192246</v>
+        <v>468.1014386381746</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>225.5</v>
+        <v>288.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>36.96207850665105</v>
+        <v>54.6053206185696</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.61871783944413</v>
+        <v>16.52758920725688</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.005076658483848</v>
+        <v>0.9322671015168928</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.3489849084228353</v>
+        <v>1.056224956175033</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6907</v>
+        <v>7402</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>442.2789580529408</v>
+        <v>455.1860943825759</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>180</v>
+        <v>100.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46.54538149888459</v>
+        <v>41.11291313334426</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.19393860610655</v>
+        <v>15.26474406961505</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7101761453099161</v>
+        <v>0.7818365222393238</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.1013033170212389</v>
+        <v>-0.8634944022999251</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8024</v>
+        <v>8028</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>441.3402960707922</v>
+        <v>444.1529791192246</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>12.8</v>
+        <v>225.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>36.63488304289069</v>
+        <v>36.96207850665105</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>13.58371838162636</v>
+        <v>20.61871783944413</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.663519068565709</v>
+        <v>1.005076658483848</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0393373963518891</v>
+        <v>-0.3489849084228353</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7610</v>
+        <v>6907</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>432.432151705162</v>
+        <v>442.2789580529408</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1975</v>
+        <v>180</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>58.36362025086166</v>
+        <v>46.54538149888459</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>18.44057906102758</v>
+        <v>16.19393860610655</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7635481366257738</v>
+        <v>0.7101761453099161</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>54.78247311913209</v>
+        <v>-0.1013033170212389</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6894</v>
+        <v>8024</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>429.105846516826</v>
+        <v>441.3402960707922</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>356</v>
+        <v>12.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>56.65384201654621</v>
+        <v>36.63488304289069</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18.60490573665348</v>
+        <v>13.58371838162636</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.079081793750921</v>
+        <v>1.663519068565709</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.399700547011793</v>
+        <v>0.0393373963518891</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7712</v>
+        <v>7610</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>422.7924988623239</v>
+        <v>432.432151705162</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>145</v>
+        <v>1975</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>44.65630857722145</v>
+        <v>58.36362025086166</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>19.7395354337804</v>
+        <v>18.44057906102758</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5757559935894052</v>
+        <v>0.7635481366257738</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.3560759082001321</v>
+        <v>54.78247311913209</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7704</v>
+        <v>6894</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>421.8333508488796</v>
+        <v>429.105846516826</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>60.5</v>
+        <v>356</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>46.80559456548413</v>
+        <v>56.65384201654621</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.5370625810025</v>
+        <v>18.60490573665348</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.671204463877441</v>
+        <v>1.079081793750921</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.2899990398773522</v>
+        <v>1.399700547011793</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6949</v>
+        <v>7712</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>398.2988449832656</v>
+        <v>422.7924988623239</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>25.45270123867219</v>
+        <v>44.65630857722145</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>41.22405142116193</v>
+        <v>19.7395354337804</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2.229884498326561</v>
+        <v>0.5757559935894052</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-134.3736029248039</v>
+        <v>-0.3560759082001321</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6859</v>
+        <v>7704</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>396.5131767013767</v>
+        <v>421.8333508488796</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>117</v>
+        <v>60.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>60.30586671805407</v>
+        <v>46.80559456548413</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>30.87776824617464</v>
+        <v>15.5370625810025</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7490308604439039</v>
+        <v>1.671204463877441</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.8483666931514913</v>
+        <v>-0.2899990398773522</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6971</v>
+        <v>6949</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>395.4517064380286</v>
+        <v>398.2988449832656</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>24.9</v>
+        <v>53</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>33.21335886428166</v>
+        <v>25.45270123867219</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>19.23189985305205</v>
+        <v>41.22405142116193</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.077346071182194</v>
+        <v>2.229884498326561</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.1085340569923121</v>
+        <v>-134.3736029248039</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7795</v>
+        <v>6859</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>395.0161982470003</v>
+        <v>396.5131767013767</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>507</v>
+        <v>117</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>48.09204036377554</v>
+        <v>60.30586671805407</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>18.15154999400956</v>
+        <v>30.87776824617464</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.057390940449529</v>
+        <v>0.7490308604439039</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-4.857002887794566</v>
+        <v>0.8483666931514913</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6931</v>
+        <v>6971</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>393.9970810819078</v>
+        <v>395.4517064380286</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>39.3</v>
+        <v>24.9</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>37.51363357572813</v>
+        <v>33.21335886428166</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.84773514341558</v>
+        <v>19.23189985305205</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9188747395547756</v>
+        <v>1.077346071182194</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.3087162992088587</v>
+        <v>-0.1085340569923121</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>7823</v>
+        <v>7795</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>391.0223139100039</v>
+        <v>395.0161982470003</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>42.87104604314708</v>
+        <v>48.09204036377554</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.86280864684662</v>
+        <v>18.15154999400956</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.254915084079311</v>
+        <v>1.057390940449529</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.4105665716864769</v>
+        <v>-4.857002887794566</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6962</v>
+        <v>6931</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>388.5185044844931</v>
+        <v>393.9970810819078</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>30.4</v>
+        <v>39.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>39.01048500204858</v>
+        <v>37.51363357572813</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>13.41130152624843</v>
+        <v>22.84773514341558</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4782405164452419</v>
+        <v>0.9188747395547756</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.0231518015644265</v>
+        <v>-0.3087162992088587</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7842</v>
+        <v>7823</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>383.7256238765445</v>
+        <v>391.0223139100039</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>54.03416638378295</v>
+        <v>42.87104604314708</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>18.26711455059856</v>
+        <v>25.86280864684662</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.9160560050785176</v>
+        <v>1.254915084079311</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.5171480144232632</v>
+        <v>-0.4105665716864769</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6952</v>
+        <v>6962</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>382.0044227201112</v>
+        <v>388.5185044844931</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>38.8</v>
+        <v>30.4</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.62857628592805</v>
+        <v>39.01048500204858</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.89534282210805</v>
+        <v>13.41130152624843</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.201041929537163</v>
+        <v>0.4782405164452419</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.5642296996544727</v>
+        <v>-0.0231518015644265</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8039</v>
+        <v>7842</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>376.6906447409778</v>
+        <v>383.7256238765445</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>272</v>
+        <v>100</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.57413105992497</v>
+        <v>54.03416638378295</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>28.08985533762192</v>
+        <v>18.26711455059856</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5690644740977797</v>
+        <v>0.9160560050785176</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-8.499367564597904</v>
+        <v>-0.5171480144232632</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7769</v>
+        <v>6952</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>369.226451853804</v>
+        <v>382.0044227201112</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>6310</v>
+        <v>38.8</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.40834322207052</v>
+        <v>52.62857628592805</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13.05967543462294</v>
+        <v>15.89534282210805</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6843873394825285</v>
+        <v>1.201041929537163</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>42.6633928578336</v>
+        <v>0.5642296996544727</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6953</v>
+        <v>8039</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>365.5948105869239</v>
+        <v>376.6906447409778</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>229.5</v>
+        <v>272</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>47.87115979626877</v>
+        <v>48.57413105992497</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>18.17533392680614</v>
+        <v>28.08985533762192</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.050137831981285</v>
+        <v>0.5690644740977797</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.6711511000183714</v>
+        <v>-8.499367564597904</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7750</v>
+        <v>7769</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>365.5171400737065</v>
+        <v>369.226451853804</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1995</v>
+        <v>6310</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>38.47954916680578</v>
+        <v>49.40834322207052</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>11.64536220982629</v>
+        <v>13.05967543462294</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.227472296308652</v>
+        <v>0.6843873394825285</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-35.20015663909408</v>
+        <v>42.6633928578336</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6890</v>
+        <v>6953</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>360.8118415829359</v>
+        <v>365.5948105869239</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>150</v>
+        <v>229.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>33.19149037116128</v>
+        <v>47.87115979626877</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>13.49871680552584</v>
+        <v>18.17533392680614</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8884269202680605</v>
+        <v>1.050137831981285</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.050340272732549</v>
+        <v>-0.6711511000183714</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6918</v>
+        <v>7750</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>359.6458323181571</v>
+        <v>365.5171400737065</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>1995</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>40.18700853787498</v>
+        <v>38.47954916680578</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>39.44090900173613</v>
+        <v>11.64536220982629</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.681881151739333</v>
+        <v>1.227472296308652</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.3794085204759125</v>
+        <v>-35.20015663909408</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7730</v>
+        <v>6890</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>358.2919727595059</v>
+        <v>360.8118415829359</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.16837188565218</v>
+        <v>33.19149037116128</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19.59351248412779</v>
+        <v>13.49871680552584</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5891458671089846</v>
+        <v>0.8884269202680605</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.612758585712363</v>
+        <v>-1.050340272732549</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6994</v>
+        <v>6918</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>354.9219741504195</v>
+        <v>359.6458323181571</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>29.35</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>19.83023306740952</v>
+        <v>40.18700853787498</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>31.27456744336226</v>
+        <v>39.44090900173613</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4.042932269364737</v>
+        <v>1.681881151739333</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.2824117578499556</v>
+        <v>-0.3794085204759125</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6967</v>
+        <v>7730</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>348.5147769681956</v>
+        <v>358.2919727595059</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>64.5</v>
+        <v>172</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>32.03767722224302</v>
+        <v>49.16837188565218</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12.94635836373626</v>
+        <v>19.59351248412779</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.751477696819559</v>
+        <v>0.5891458671089846</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.9038243502198866</v>
+        <v>-0.612758585712363</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6863</v>
+        <v>6994</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>345.0254987923712</v>
+        <v>354.9219741504195</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>91.2</v>
+        <v>29.35</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>23.08889104254594</v>
+        <v>19.83023306740952</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.13111436876354</v>
+        <v>31.27456744336226</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.867981947575553</v>
+        <v>4.042932269364737</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-1.65214660223499</v>
+        <v>-0.2824117578499556</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8038</v>
+        <v>6967</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>344.7334927764309</v>
+        <v>348.5147769681956</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>29.8</v>
+        <v>64.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>35.29401177780386</v>
+        <v>32.03767722224302</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>22.81920553605747</v>
+        <v>12.94635836373626</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.798409693067103</v>
+        <v>1.751477696819559</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.064451958763299</v>
+        <v>-0.9038243502198866</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6862</v>
+        <v>6863</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>339.543798845913</v>
+        <v>345.0254987923712</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>133</v>
+        <v>91.2</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>36.54506448050489</v>
+        <v>23.08889104254594</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.05479409265297</v>
+        <v>20.13111436876354</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9206867528825587</v>
+        <v>2.867981947575553</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1160108895193205</v>
+        <v>-1.65214660223499</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7734</v>
+        <v>8038</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>338.9904836844496</v>
+        <v>344.7334927764309</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2580</v>
+        <v>29.8</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>38.07091757166474</v>
+        <v>35.29401177780386</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15.37805042507551</v>
+        <v>22.81920553605747</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.919328172292113</v>
+        <v>1.798409693067103</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-9.809400686324013</v>
+        <v>0.064451958763299</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7855</v>
+        <v>6862</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>337.1078811818187</v>
+        <v>339.543798845913</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>42.1</v>
+        <v>133</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>17.63183303889592</v>
+        <v>36.54506448050489</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>54.41231974150784</v>
+        <v>15.05479409265297</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5341974601999703</v>
+        <v>0.9206867528825587</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>1.805472991142988</v>
+        <v>0.1160108895193205</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6944</v>
+        <v>7734</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>334.307845485705</v>
+        <v>338.9904836844496</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>690</v>
+        <v>2580</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>37.78570765848813</v>
+        <v>38.07091757166474</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>23.84321714569224</v>
+        <v>15.37805042507551</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.492841718058128</v>
+        <v>1.919328172292113</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>4.793254328338868</v>
+        <v>-9.809400686324013</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8033</v>
+        <v>7855</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>333.9299497991164</v>
+        <v>337.1078811818187</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>172.5</v>
+        <v>42.1</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>43.66749260483052</v>
+        <v>17.63183303889592</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>9.582140100034948</v>
+        <v>54.41231974150784</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.199544517329615</v>
+        <v>0.5341974601999703</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.491316138534647</v>
+        <v>1.805472991142988</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6916</v>
+        <v>6944</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>329.0232970075491</v>
+        <v>334.307845485705</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>18.5</v>
+        <v>690</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>46.75049165440257</v>
+        <v>37.78570765848813</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14.7858873642027</v>
+        <v>23.84321714569224</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4124519162273828</v>
+        <v>1.492841718058128</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0494368644571271</v>
+        <v>4.793254328338868</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6922</v>
+        <v>8033</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>322.2932035970019</v>
+        <v>333.9299497991164</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>186</v>
+        <v>172.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>41.46016825997208</v>
+        <v>43.66749260483052</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>22.2519891057021</v>
+        <v>9.582140100034948</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3085407365827545</v>
+        <v>1.199544517329615</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-2.846010506008783</v>
+        <v>-1.491316138534647</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6958</v>
+        <v>6916</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>322.1734569912145</v>
+        <v>329.0232970075491</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>17.3</v>
+        <v>18.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45.25349405441763</v>
+        <v>46.75049165440257</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>17.18202759559998</v>
+        <v>14.7858873642027</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.95887657869468</v>
+        <v>0.4124519162273828</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0053100526924691</v>
+        <v>0.0494368644571271</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7738</v>
+        <v>6922</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>320.4057567512293</v>
+        <v>322.2932035970019</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>164.5</v>
+        <v>186</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>40.81410238486528</v>
+        <v>41.46016825997208</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>30.25563937877498</v>
+        <v>22.2519891057021</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.7585318631696663</v>
+        <v>0.3085407365827545</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.7012348091636547</v>
+        <v>-2.846010506008783</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7728</v>
+        <v>6958</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>317.3989937939243</v>
+        <v>322.1734569912145</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>616</v>
+        <v>17.3</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>48.99226894055895</v>
+        <v>45.25349405441763</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>16.26100029423832</v>
+        <v>17.18202759559998</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.9050586798092884</v>
+        <v>0.95887657869468</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.1302264704553626</v>
+        <v>0.0053100526924691</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7556</v>
+        <v>7738</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>312.8772329891019</v>
+        <v>320.4057567512293</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>243</v>
+        <v>164.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.07836719105845</v>
+        <v>40.81410238486528</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>24.84070238611547</v>
+        <v>30.25563937877498</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6664782845839932</v>
+        <v>0.7585318631696663</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-1.03747614132361</v>
+        <v>-0.7012348091636547</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7822</v>
+        <v>7728</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>308.2733291673773</v>
+        <v>317.3989937939243</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>834</v>
+        <v>616</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>38.37540623080236</v>
+        <v>48.99226894055895</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.49898556993606</v>
+        <v>16.26100029423832</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6643790118325749</v>
+        <v>0.9050586798092884</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-7.383053721309878</v>
+        <v>-0.1302264704553626</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6908</v>
+        <v>7556</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>301.144200835043</v>
+        <v>312.8772329891019</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>29.95</v>
+        <v>243</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>33.48116282969472</v>
+        <v>48.07836719105845</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>26.75757479184526</v>
+        <v>24.84070238611547</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.239463601532567</v>
+        <v>0.6664782845839932</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1483202900842763</v>
+        <v>-1.03747614132361</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6903</v>
+        <v>7822</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>299.9615792824198</v>
+        <v>308.2733291673773</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>296.5</v>
+        <v>834</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>38.67717988228718</v>
+        <v>38.37540623080236</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>14.45712662464789</v>
+        <v>10.49898556993606</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7232426306419221</v>
+        <v>0.6643790118325749</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.2387748546256229</v>
+        <v>-7.383053721309878</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8034</v>
+        <v>6908</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>298.2281443955474</v>
+        <v>301.144200835043</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>19.75</v>
+        <v>29.95</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.46592062620438</v>
+        <v>33.48116282969472</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>25.87357721930386</v>
+        <v>26.75757479184526</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4849348773257854</v>
+        <v>0.239463601532567</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0983545570630128</v>
+        <v>0.1483202900842763</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8016</v>
+        <v>6903</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>297.1483433650295</v>
+        <v>299.9615792824198</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>277.5</v>
+        <v>296.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>40.68301824600224</v>
+        <v>38.67717988228718</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>11.58588984299252</v>
+        <v>14.45712662464789</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7253601440817212</v>
+        <v>0.7232426306419221</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-1.810568031678458</v>
+        <v>0.2387748546256229</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6936</v>
+        <v>8034</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>295.6820965172324</v>
+        <v>298.2281443955474</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>31.7</v>
+        <v>19.75</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>37.65377079409132</v>
+        <v>50.46592062620438</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>35.70844298972026</v>
+        <v>25.87357721930386</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.491601034581691</v>
+        <v>0.4849348773257854</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.07457985491935799</v>
+        <v>0.0983545570630128</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7715</v>
+        <v>8016</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>291.4695034541402</v>
+        <v>297.1483433650295</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>27.7</v>
+        <v>277.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>30.49925940546957</v>
+        <v>40.68301824600224</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>27.52506834203832</v>
+        <v>11.58588984299252</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.9558675259834962</v>
+        <v>0.7253601440817212</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.124612191612657</v>
+        <v>-1.810568031678458</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6951</v>
+        <v>6936</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>291.0046270384801</v>
+        <v>295.6820965172324</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>70.2</v>
+        <v>31.7</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>33.3659081320978</v>
+        <v>37.65377079409132</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>27.38959100431273</v>
+        <v>35.70844298972026</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.395013379887703</v>
+        <v>1.491601034581691</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0550527229869811</v>
+        <v>-0.07457985491935799</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4449,21 +4449,21 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6965</v>
+        <v>7715</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>287.3589129980887</v>
+        <v>291.4695034541402</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>69.8</v>
+        <v>27.7</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>27.00319298669245</v>
+        <v>30.49925940546957</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>36.92657867887691</v>
+        <v>27.52506834203832</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>3.135891299808875</v>
+        <v>0.9558675259834962</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.2657067412913059</v>
+        <v>-0.124612191612657</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7689</v>
+        <v>6951</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>276.7651766630884</v>
+        <v>291.0046270384801</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>156.5</v>
+        <v>70.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>24.9825487722802</v>
+        <v>33.3659081320978</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>26.14070131470856</v>
+        <v>27.38959100431273</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.8030051862625336</v>
+        <v>1.395013379887703</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.5433249873843531</v>
+        <v>-0.0550527229869811</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4555,21 +4555,21 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7751</v>
+        <v>6965</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>272.8220767731365</v>
+        <v>287.3589129980887</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>1425</v>
+        <v>69.8</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45.0783817083227</v>
+        <v>27.00319298669245</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>14.22502048495799</v>
+        <v>36.92657867887691</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3186407139781213</v>
+        <v>3.135891299808875</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-34.90035957100645</v>
+        <v>-0.2657067412913059</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6919</v>
+        <v>7689</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>272.7264536994814</v>
+        <v>276.7651766630884</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>79.5</v>
+        <v>156.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>31.07841498388281</v>
+        <v>24.9825487722802</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>29.4617183318875</v>
+        <v>26.14070131470856</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.7267323666430254</v>
+        <v>0.8030051862625336</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-1.717434204458955</v>
+        <v>-0.5433249873843531</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7805</v>
+        <v>7751</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>270.7821799942589</v>
+        <v>272.8220767731365</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>495</v>
+        <v>1425</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>29.84495571605304</v>
+        <v>45.0783817083227</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>38.14876621441928</v>
+        <v>14.22502048495799</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.8345404438181742</v>
+        <v>0.3186407139781213</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-1.780427596257923</v>
+        <v>-34.90035957100645</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6838</v>
+        <v>6919</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>267.0005112363373</v>
+        <v>272.7264536994814</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>23.6</v>
+        <v>79.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>49.85052492231557</v>
+        <v>31.07841498388281</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>19.84052584458855</v>
+        <v>29.4617183318875</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.9021152101812726</v>
+        <v>0.7267323666430254</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0815679884887465</v>
+        <v>-1.717434204458955</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7839</v>
+        <v>7805</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>266.2420147580638</v>
+        <v>270.7821799942589</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>42.15</v>
+        <v>495</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>33.86997850948285</v>
+        <v>29.84495571605304</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>41.60566435563781</v>
+        <v>38.14876621441928</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.839595315058142</v>
+        <v>0.8345404438181742</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.1555363091710141</v>
+        <v>-1.780427596257923</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6921</v>
+        <v>6838</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>264.416077952109</v>
+        <v>267.0005112363373</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>61</v>
+        <v>23.6</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>37.06295331593567</v>
+        <v>49.85052492231557</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>23.02795190794816</v>
+        <v>19.84052584458855</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.526163478992923</v>
+        <v>0.9021152101812726</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.5025349761787857</v>
+        <v>0.0815679884887465</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6902</v>
+        <v>7839</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>261.485919144396</v>
+        <v>266.2420147580638</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>121</v>
+        <v>42.15</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>39.55342890891564</v>
+        <v>33.86997850948285</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>10.39684673057898</v>
+        <v>41.60566435563781</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.239558325209048</v>
+        <v>0.839595315058142</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.3790917354286603</v>
+        <v>-0.1555363091710141</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7721</v>
+        <v>6921</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>258.3004905179182</v>
+        <v>264.416077952109</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>59.2</v>
+        <v>61</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>39.58516618233659</v>
+        <v>37.06295331593567</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13.36526153981109</v>
+        <v>23.02795190794816</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.422097541810571</v>
+        <v>0.526163478992923</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0292826336663434</v>
+        <v>-0.5025349761787857</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8032</v>
+        <v>6902</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>252.9314219898194</v>
+        <v>261.485919144396</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>34.65</v>
+        <v>121</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>34.67095119305796</v>
+        <v>39.55342890891564</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>22.58998589912511</v>
+        <v>10.39684673057898</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6956750115467863</v>
+        <v>1.239558325209048</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0492489623328596</v>
+        <v>-0.3790917354286603</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6855</v>
+        <v>7721</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>251.3925937190821</v>
+        <v>258.3004905179182</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>115</v>
+        <v>59.2</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.97471946996773</v>
+        <v>39.58516618233659</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8.518779298880146</v>
+        <v>13.36526153981109</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.110272238752942</v>
+        <v>1.422097541810571</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>6.617954972777737</v>
+        <v>0.0292826336663434</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>7820</v>
+        <v>8032</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>245.6314116917102</v>
+        <v>252.9314219898194</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>110</v>
+        <v>34.65</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>38.94525553412685</v>
+        <v>34.67095119305796</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17.67389577798503</v>
+        <v>22.58998589912511</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>2.114257248908032</v>
+        <v>0.6956750115467863</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-1.242662373025745</v>
+        <v>-0.0492489623328596</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6877</v>
+        <v>6855</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>245.0669687914249</v>
+        <v>251.3925937190821</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>42.29969879505997</v>
+        <v>51.97471946996773</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>17.88191197870405</v>
+        <v>8.518779298880146</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.4575737059748964</v>
+        <v>1.110272238752942</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>1</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.3047654101343724</v>
+        <v>6.617954972777737</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6854</v>
+        <v>7820</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>244.4100709331946</v>
+        <v>245.6314116917102</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>110</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>40.86944396647751</v>
+        <v>38.94525553412685</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>16.87309379764291</v>
+        <v>17.67389577798503</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.7247958465462306</v>
+        <v>2.114257248908032</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1267167211505691</v>
+        <v>-1.242662373025745</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6934</v>
+        <v>6877</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>242.2736980494346</v>
+        <v>245.0669687914249</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>112</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>51.49971915948845</v>
+        <v>42.29969879505997</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.65065623838358</v>
+        <v>17.88191197870405</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.9481385102628328</v>
+        <v>0.4575737059748964</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.2579618258063493</v>
+        <v>0.3047654101343724</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7722</v>
+        <v>6854</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>241.4052335087498</v>
+        <v>244.4100709331946</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>261.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>35.17802066689205</v>
+        <v>40.86944396647751</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>10.67707531486638</v>
+        <v>16.87309379764291</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.983642516921534</v>
+        <v>0.7247958465462306</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-1.441081666701278</v>
+        <v>0.1267167211505691</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>7803</v>
+        <v>6934</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>240.6263180925809</v>
+        <v>242.2736980494346</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>19.05</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>41.18638410408759</v>
+        <v>51.49971915948845</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9.580484768405066</v>
+        <v>17.65065623838358</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.790833257535525</v>
+        <v>0.9481385102628328</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.076709390732975</v>
+        <v>0.2579618258063493</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7791</v>
+        <v>7722</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>239.967327074938</v>
+        <v>241.4052335087498</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>55.3</v>
+        <v>261.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>35.72726465483494</v>
+        <v>35.17802066689205</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>29.47695148744664</v>
+        <v>10.67707531486638</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.7372048966424979</v>
+        <v>1.983642516921534</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.09671600977104911</v>
+        <v>-1.441081666701278</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6914</v>
+        <v>7803</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>239.8848287854871</v>
+        <v>240.6263180925809</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>120</v>
+        <v>19.05</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>20.28449379277681</v>
+        <v>41.18638410408759</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>40.17518474684081</v>
+        <v>9.580484768405066</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.345442150155212</v>
+        <v>1.790833257535525</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.6005484361822937</v>
+        <v>0.076709390732975</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7818</v>
+        <v>7791</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>238.8968861127971</v>
+        <v>239.967327074938</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>60</v>
+        <v>55.3</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>34.02086412567229</v>
+        <v>35.72726465483494</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.94804406709902</v>
+        <v>29.47695148744664</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.128357703594091</v>
+        <v>0.7372048966424979</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0925285633634631</v>
+        <v>0.09671600977104911</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7768</v>
+        <v>6914</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>238.7208014011896</v>
+        <v>239.8848287854871</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>263</v>
+        <v>120</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>38.73799868648237</v>
+        <v>20.28449379277681</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.06005831978867</v>
+        <v>40.17518474684081</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6598429065703898</v>
+        <v>0.345442150155212</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-1.524784059412704</v>
+        <v>-0.6005484361822937</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6910</v>
+        <v>7818</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>235.8124302952436</v>
+        <v>238.8968861127971</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>24.7</v>
+        <v>60</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>47.69551216109102</v>
+        <v>34.02086412567229</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.80517322071372</v>
+        <v>16.94804406709902</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.427522622502988</v>
+        <v>1.128357703594091</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0533107652789456</v>
+        <v>0.0925285633634631</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6865</v>
+        <v>7768</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>231.3331380454106</v>
+        <v>238.7208014011896</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>25.2</v>
+        <v>263</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>52.27564939134591</v>
+        <v>38.73799868648237</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>8.595055285439731</v>
+        <v>17.06005831978867</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.9307709860362088</v>
+        <v>0.6598429065703898</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.172459442305521</v>
+        <v>-1.524784059412704</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6955</v>
+        <v>6910</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>227.0040737068366</v>
+        <v>235.8124302952436</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>99</v>
+        <v>24.7</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>46.23052671629149</v>
+        <v>47.69551216109102</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>7.755345706051234</v>
+        <v>17.80517322071372</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.1035664266998795</v>
+        <v>1.427522622502988</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.028007816019149</v>
+        <v>0.0533107652789456</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7786</v>
+        <v>6865</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>224.6146023650372</v>
+        <v>231.3331380454106</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>115</v>
+        <v>25.2</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>34.95094155366392</v>
+        <v>52.27564939134591</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>21.79970361565185</v>
+        <v>8.595055285439731</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.436832715535513</v>
+        <v>0.9307709860362088</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.2430319236201557</v>
+        <v>0.172459442305521</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6996</v>
+        <v>6955</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>216.5675826472864</v>
+        <v>227.0040737068366</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>165</v>
+        <v>99</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>33.21814070325466</v>
+        <v>46.23052671629149</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.4895038792889</v>
+        <v>7.755345706051234</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7490881239523627</v>
+        <v>0.1035664266998795</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-1.551647834553796</v>
+        <v>-1.028007816019149</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7547</v>
+        <v>7786</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>207.8689238760561</v>
+        <v>224.6146023650372</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>48.5</v>
+        <v>115</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>36.58938137258418</v>
+        <v>34.95094155366392</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>10.950605889377</v>
+        <v>21.79970361565185</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.2744011195565678</v>
+        <v>1.436832715535513</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.2062313329017707</v>
+        <v>-0.2430319236201557</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7749</v>
+        <v>6996</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>206.3957349101741</v>
+        <v>216.5675826472864</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>349.5</v>
+        <v>165</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>43.35791735089775</v>
+        <v>33.21814070325466</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>14.89673896194326</v>
+        <v>17.4895038792889</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.7829523241422622</v>
+        <v>0.7490881239523627</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.6883114855844652</v>
+        <v>-1.551647834553796</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7740</v>
+        <v>7547</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>203.8369178279058</v>
+        <v>207.8689238760561</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>129</v>
+        <v>48.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>40.02234753887275</v>
+        <v>36.58938137258418</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>12.4314481816693</v>
+        <v>10.950605889377</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2.196213972897082</v>
+        <v>0.2744011195565678</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.2401009108561567</v>
+        <v>-0.2062313329017707</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6899</v>
+        <v>7749</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>197.1911360799466</v>
+        <v>206.3957349101741</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>49.5</v>
+        <v>349.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>36.74027337662746</v>
+        <v>43.35791735089775</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>20.62865343023498</v>
+        <v>14.89673896194326</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.109134520356214</v>
+        <v>0.7829523241422622</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.08690362984441539</v>
+        <v>-0.6883114855844652</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7747</v>
+        <v>7740</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>191.5468157057116</v>
+        <v>203.8369178279058</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>112.5</v>
+        <v>129</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>51.79003175023304</v>
+        <v>40.02234753887275</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>8.362525567479999</v>
+        <v>12.4314481816693</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.1564682237790823</v>
+        <v>2.196213972897082</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.4797769246281316</v>
+        <v>0.2401009108561567</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6873</v>
+        <v>6899</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>188.2457430346613</v>
+        <v>197.1911360799466</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>49.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>37.06424028218698</v>
+        <v>36.74027337662746</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>21.73249542990695</v>
+        <v>20.62865343023498</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.639290178946045</v>
+        <v>1.109134520356214</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.4634963302439452</v>
+        <v>0.08690362984441539</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6928</v>
+        <v>7747</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>184.9724283232393</v>
+        <v>191.5468157057116</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>46.05</v>
+        <v>112.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>39.10010461663875</v>
+        <v>51.79003175023304</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.83908913521626</v>
+        <v>8.362525567479999</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.022952912492905</v>
+        <v>0.1564682237790823</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0230380330937505</v>
+        <v>-0.4797769246281316</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6901</v>
+        <v>6873</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>183.4322562824066</v>
+        <v>188.2457430346613</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14.75</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>36.21117165954799</v>
+        <v>37.06424028218698</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.01133839121388</v>
+        <v>21.73249542990695</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.6002705498770193</v>
+        <v>0.639290178946045</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0784602153978386</v>
+        <v>0.4634963302439452</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7780</v>
+        <v>6928</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>180.6460060847623</v>
+        <v>184.9724283232393</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>16.4</v>
+        <v>46.05</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>38.37041501215057</v>
+        <v>39.10010461663875</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>14.94419670932501</v>
+        <v>11.83908913521626</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.9671192555606782</v>
+        <v>1.022952912492905</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0180183129420051</v>
+        <v>-0.0230380330937505</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>7760</v>
+        <v>6901</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>176.5656760572898</v>
+        <v>183.4322562824066</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>32.5</v>
+        <v>14.75</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>35.85955547024967</v>
+        <v>36.21117165954799</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>8.350076896402671</v>
+        <v>15.01133839121388</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.6080721615390883</v>
+        <v>0.6002705498770193</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0189224527670813</v>
+        <v>-0.0784602153978386</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6869</v>
+        <v>7780</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>176.1022482347245</v>
+        <v>180.6460060847623</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>63.5</v>
+        <v>16.4</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>39.22997045587395</v>
+        <v>38.37041501215057</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>10.96755399909235</v>
+        <v>14.94419670932501</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.8732615158237539</v>
+        <v>0.9671192555606782</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.2499438383290005</v>
+        <v>-0.0180183129420051</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8011</v>
+        <v>7760</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>175.3266095618374</v>
+        <v>176.5656760572898</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>15.55</v>
+        <v>32.5</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>38.66154302541228</v>
+        <v>35.85955547024967</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>24.17557427824885</v>
+        <v>8.350076896402671</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.097500851468217</v>
+        <v>0.6080721615390883</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0137655006910853</v>
+        <v>-0.0189224527670813</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>7821</v>
+        <v>6869</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>170.3020076704397</v>
+        <v>176.1022482347245</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>38.9</v>
+        <v>63.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>41.25298301171847</v>
+        <v>39.22997045587395</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12.41567192662211</v>
+        <v>10.96755399909235</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.7593200346376014</v>
+        <v>0.8732615158237539</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0909976054070229</v>
+        <v>-0.2499438383290005</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>7753</v>
+        <v>8011</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>166.0571223164618</v>
+        <v>175.3266095618374</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>36.2</v>
+        <v>15.55</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>37.07222792492158</v>
+        <v>38.66154302541228</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>9.451475259546203</v>
+        <v>24.17557427824885</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.8243769480987101</v>
+        <v>1.097500851468217</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0674118956604469</v>
+        <v>-0.0137655006910853</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6947</v>
+        <v>7821</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>164.4224884059077</v>
+        <v>170.3020076704397</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>38.9</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>38.14062936629125</v>
+        <v>41.25298301171847</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>8.351324998023175</v>
+        <v>12.41567192662211</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5495827477633887</v>
+        <v>0.7593200346376014</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.2894227884753029</v>
+        <v>0.0909976054070229</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7736</v>
+        <v>7753</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>161.8108236384255</v>
+        <v>166.0571223164618</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>36.2</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>44.55841800746531</v>
+        <v>37.07222792492158</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12.5387030231549</v>
+        <v>9.451475259546203</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.2027191393896802</v>
+        <v>0.8243769480987101</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0465163136908648</v>
+        <v>0.0674118956604469</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7770</v>
+        <v>6947</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>160.0408819466052</v>
+        <v>164.4224884059077</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>36.05</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>49.38841309106509</v>
+        <v>38.14062936629125</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>5.156210709937552</v>
+        <v>8.351324998023175</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.6502922456406861</v>
+        <v>0.5495827477633887</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0467989166561217</v>
+        <v>0.2894227884753029</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6988</v>
+        <v>7736</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>151.0239793808995</v>
+        <v>161.8108236384255</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>11.9</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>49.47701235507736</v>
+        <v>44.55841800746531</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>8.669354644960396</v>
+        <v>12.5387030231549</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5249125692501843</v>
+        <v>0.2027191393896802</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.06974282379087531</v>
+        <v>0.0465163136908648</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6923</v>
+        <v>7770</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>148.1899998770923</v>
+        <v>160.0408819466052</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>76.3</v>
+        <v>36.05</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>49.61567520738405</v>
+        <v>49.38841309106509</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>8.82503113935787</v>
+        <v>5.156210709937552</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.341228325338093</v>
+        <v>0.6502922456406861</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0283119010568708</v>
+        <v>0.0467989166561217</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>7827</v>
+        <v>6988</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>138.8847476145313</v>
+        <v>151.0239793808995</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>152.5</v>
+        <v>11.9</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.67021962935411</v>
+        <v>49.47701235507736</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>12.15770209932584</v>
+        <v>8.669354644960396</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.6033566616965949</v>
+        <v>0.5249125692501843</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.5344806030238305</v>
+        <v>0.06974282379087531</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7765</v>
+        <v>6923</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>136.5778561722491</v>
+        <v>148.1899998770923</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>218.5</v>
+        <v>76.3</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>40.09576238256078</v>
+        <v>49.61567520738405</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>19.91073562925259</v>
+        <v>8.82503113935787</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>2.2775312941229</v>
+        <v>1.341228325338093</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.6182219607842137</v>
+        <v>0.0283119010568708</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7732</v>
+        <v>7827</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>124.3858180887572</v>
+        <v>138.8847476145313</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>33.5</v>
+        <v>152.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>44.97102192679844</v>
+        <v>45.67021962935411</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>6.548895520443521</v>
+        <v>12.15770209932584</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.6068260343539389</v>
+        <v>0.6033566616965949</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0527645073205546</v>
+        <v>-0.5344806030238305</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6997</v>
+        <v>7765</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>112.9366518360455</v>
+        <v>136.5778561722491</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>0</v>
+        <v>218.5</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>40.78126992313038</v>
+        <v>40.09576238256078</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>9.327130690366822</v>
+        <v>19.91073562925259</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0</v>
+        <v>2.2775312941229</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,62 +7089,168 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-6.155984697737841</v>
+        <v>-0.6182219607842137</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
+        <v>7732</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>金興精密</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>124.3858180887572</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>44.97102192679844</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>6.548895520443521</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.6068260343539389</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.0527645073205546</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>6997</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>博弘</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>112.9366518360455</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>40.78126992313038</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>9.327130690366822</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-6.155984697737841</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
         <v>7705</v>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>三商餐飲</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D126" s="2" t="n">
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>86.97740281809624</v>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E128" s="2" t="n">
         <v>29.95</v>
       </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H126" s="2" t="n">
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
         <v>42.79036847637541</v>
       </c>
-      <c r="I126" s="2" t="n">
+      <c r="I128" s="2" t="n">
         <v>13.8034326521969</v>
       </c>
-      <c r="J126" s="2" t="n">
+      <c r="J128" s="2" t="n">
         <v>0.4190293919422965</v>
       </c>
-      <c r="K126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N126" s="2" t="n">
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
         <v>-0.0444045562363211</v>
       </c>
-      <c r="O126" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
